--- a/tests/agent_contract/data/S7_two_dims.xlsx
+++ b/tests/agent_contract/data/S7_two_dims.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +413,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C193"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>产品类别</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>产品类别</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4224</v>
       </c>
     </row>
     <row r="3">
@@ -452,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3664</v>
+        <v>7223</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6878</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6405</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2561</v>
+        <v>5505</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3487</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +535,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4282</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7007</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="10">
@@ -557,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6838</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +580,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3345</v>
+        <v>7425</v>
       </c>
     </row>
     <row r="12">
@@ -587,7 +595,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6703</v>
+        <v>39836</v>
       </c>
     </row>
     <row r="13">
@@ -598,11 +606,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4592</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="14">
@@ -613,11 +621,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2634</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="15">
@@ -628,11 +636,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2570</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="16">
@@ -643,11 +651,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5769</v>
+        <v>7559</v>
       </c>
     </row>
     <row r="17">
@@ -658,11 +666,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6652</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="18">
@@ -673,11 +681,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5347</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="19">
@@ -688,11 +696,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2167</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="20">
@@ -703,11 +711,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2072</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="21">
@@ -718,11 +726,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2027</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="22">
@@ -737,7 +745,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5632</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="23">
@@ -752,7 +760,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3370</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="24">
@@ -767,7 +775,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7113</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="25">
@@ -782,7 +790,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2000</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +805,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6378</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="27">
@@ -812,7 +820,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2945</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="28">
@@ -823,11 +831,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5822</v>
+        <v>6587</v>
       </c>
     </row>
     <row r="29">
@@ -838,11 +846,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5896</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="30">
@@ -853,11 +861,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2512</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="31">
@@ -868,11 +876,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5626</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="32">
@@ -883,11 +891,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6662</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="33">
@@ -898,11 +906,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8044</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="34">
@@ -917,7 +925,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7775</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="35">
@@ -932,7 +940,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2574</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="36">
@@ -947,7 +955,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4355</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="37">
@@ -962,7 +970,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2218</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="38">
@@ -977,7 +985,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2056</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="39">
@@ -992,7 +1000,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2453</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="40">
@@ -1007,7 +1015,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2091</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="41">
@@ -1022,7 +1030,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="42">
@@ -1037,7 +1045,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2054</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43">
@@ -1052,7 +1060,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44">
@@ -1067,7 +1075,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45">
@@ -1108,11 +1116,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2000</v>
+        <v>5011</v>
       </c>
     </row>
     <row r="48">
@@ -1123,11 +1131,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2000</v>
+        <v>5935</v>
       </c>
     </row>
     <row r="49">
@@ -1138,11 +1146,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2000</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="50">
@@ -1153,11 +1161,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2000</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="51">
@@ -1168,11 +1176,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2000</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="52">
@@ -1183,7 +1191,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1202,7 +1210,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2429</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="54">
@@ -1217,7 +1225,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4156</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="55">
@@ -1232,7 +1240,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2347</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="56">
@@ -1247,7 +1255,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3618</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57">
@@ -1262,7 +1270,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3662</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="58">
@@ -1277,7 +1285,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="59">
@@ -1292,7 +1300,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="60">
@@ -1307,97 +1315,97 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2003</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2008</v>
+        <v>7958</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2000</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2000</v>
+        <v>5159</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2000</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2000</v>
+        <v>6019</v>
       </c>
     </row>
     <row r="67">
@@ -1412,7 +1420,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3128</v>
+        <v>6724</v>
       </c>
     </row>
     <row r="68">
@@ -1427,7 +1435,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2522</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="69">
@@ -1442,7 +1450,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7981</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="70">
@@ -1457,7 +1465,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3103</v>
+        <v>16794</v>
       </c>
     </row>
     <row r="71">
@@ -1468,11 +1476,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7937</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="72">
@@ -1483,11 +1491,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7942</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="73">
@@ -1498,11 +1506,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5221</v>
+        <v>7865</v>
       </c>
     </row>
     <row r="74">
@@ -1513,11 +1521,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7986</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="75">
@@ -1528,11 +1536,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2444</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="76">
@@ -1543,11 +1551,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3544</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="77">
@@ -1558,11 +1566,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20192</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="78">
@@ -1577,7 +1585,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5596</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="79">
@@ -1592,7 +1600,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4927</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="80">
@@ -1607,7 +1615,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6873</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="81">
@@ -1622,7 +1630,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3106</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="82">
@@ -1637,7 +1645,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7142</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="83">
@@ -1652,7 +1660,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6775</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="84">
@@ -1667,7 +1675,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2218</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="85">
@@ -1682,7 +1690,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3208</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="86">
@@ -1697,7 +1705,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2006</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="87">
@@ -1712,7 +1720,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3879</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="88">
@@ -1727,7 +1735,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2162</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="89">
@@ -1742,7 +1750,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2070</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="90">
@@ -1753,11 +1761,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2021</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="91">
@@ -1768,11 +1776,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2010</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="92">
@@ -1783,11 +1791,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2003</v>
+        <v>7219</v>
       </c>
     </row>
     <row r="93">
@@ -1798,11 +1806,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2004</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="94">
@@ -1817,7 +1825,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7995</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="95">
@@ -1832,7 +1840,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6253</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="96">
@@ -1847,7 +1855,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2520</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="97">
@@ -1862,7 +1870,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2296</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="98">
@@ -1877,7 +1885,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2240</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="99">
@@ -1892,7 +1900,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="100">
@@ -1907,7 +1915,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2000</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="101">
@@ -1918,11 +1926,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2398</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="102">
@@ -1933,11 +1941,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="103">
@@ -1948,11 +1956,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2102</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="104">
@@ -1963,11 +1971,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2071</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="105">
@@ -1978,11 +1986,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2093</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="106">
@@ -1993,11 +2001,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="107">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2023,11 +2031,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="109">
@@ -2132,187 +2140,187 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2000</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2000</v>
+        <v>5973</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2000</v>
+        <v>5255</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2000</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2000</v>
+        <v>6783</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2000</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2000</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2000</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2000</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2000</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2000</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-8000</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="128">
@@ -2327,7 +2335,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2166</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="129">
@@ -2342,7 +2350,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6525</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="130">
@@ -2357,7 +2365,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4886</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="131">
@@ -2372,7 +2380,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2977</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="132">
@@ -2383,11 +2391,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>5680</v>
+        <v>4923</v>
       </c>
     </row>
     <row r="133">
@@ -2398,11 +2406,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7741</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="134">
@@ -2413,11 +2421,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2967</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="135">
@@ -2428,11 +2436,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6386</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="136">
@@ -2443,11 +2451,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5439</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="137">
@@ -2458,11 +2466,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2637</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="138">
@@ -2473,11 +2481,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2402</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="139">
@@ -2488,11 +2496,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5274</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="140">
@@ -2503,11 +2511,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5281</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="141">
@@ -2518,11 +2526,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2444</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="142">
@@ -2533,11 +2541,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2357</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="143">
@@ -2548,11 +2556,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2838</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="144">
@@ -2567,7 +2575,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2361</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="145">
@@ -2582,7 +2590,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>7141</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="146">
@@ -2597,7 +2605,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4537</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="147">
@@ -2612,7 +2620,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5135</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="148">
@@ -2627,7 +2635,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2174</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="149">
@@ -2642,7 +2650,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2594</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="150">
@@ -2657,7 +2665,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="151">
@@ -2668,11 +2676,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2003</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="152">
@@ -2683,11 +2691,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2000</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="153">
@@ -2698,11 +2706,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2004</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="154">
@@ -2713,11 +2721,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2001</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="155">
@@ -2728,11 +2736,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2000</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="156">
@@ -2743,11 +2751,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2000</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="157">
@@ -2758,11 +2766,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2000</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="158">
@@ -2773,11 +2781,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="159">
@@ -2788,11 +2796,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="160">
@@ -2803,7 +2811,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2818,7 +2826,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2833,7 +2841,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2848,7 +2856,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2867,7 +2875,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3106</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="165">
@@ -2882,7 +2890,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4030</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="166">
@@ -2897,7 +2905,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3884</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="167">
@@ -2908,11 +2916,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2253</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="168">
@@ -2923,11 +2931,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2515</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="169">
@@ -2938,11 +2946,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2057</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="170">
@@ -2953,11 +2961,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2022</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="171">
@@ -2968,11 +2976,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="172">
@@ -2983,11 +2991,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2110</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="173">
@@ -2998,11 +3006,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2012</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="174">
@@ -3013,11 +3021,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="175">
@@ -3028,11 +3036,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="176">
@@ -3043,7 +3051,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3058,7 +3066,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3073,236 +3081,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>服装鞋帽</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
